--- a/.dod/evidence/DOD-rol-1-definition-of-done-d5c6584cb7/panorama-SC-2026-07-21.xlsx
+++ b/.dod/evidence/DOD-rol-1-definition-of-done-d5c6584cb7/panorama-SC-2026-07-21.xlsx
@@ -47,7 +47,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -55,21 +55,15 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <bottom style="thin">
-        <color rgb="008B7355"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,142 +458,6 @@
           <t>Período</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Dispensa</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>181</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>1554316.71</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>8587.385138121546</v>
-      </c>
-      <c r="E2" s="2" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Pregão - Eletrônico</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>136</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>172524320</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>1268561.176470588</v>
-      </c>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Inexigibilidade</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>16177674.35</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>202220.929375</v>
-      </c>
-      <c r="E4" s="2" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Concorrência - Eletrônica</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>96223856.90000001</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>4183645.952173913</v>
-      </c>
-      <c r="E5" s="2" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Credenciamento</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>18317560.88</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>1144847.555</v>
-      </c>
-      <c r="E6" s="2" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Pregão - Presencial</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>1885031.29</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>471257.8225</v>
-      </c>
-      <c r="E7" s="2" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Concorrência - Presencial</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>501893.99</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>501893.99</v>
-      </c>
-      <c r="E8" s="2" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Leilão - Eletrônico</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>210310</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>210310</v>
-      </c>
-      <c r="E9" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -612,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -635,326 +493,6 @@
         <is>
           <t>Órgãos</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Florianópolis</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>86844858.09999999</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Jaraguá do Sul</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>1739289.74</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Maravilha</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>57184.63</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>São Miguel do Oeste</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>22443730.87</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Brusque</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>2661025.54</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Timbó</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>68405.74000000001</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Chapecó</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>3270106.74</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>São Lourenço do Oeste</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>18332.32</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Capinzal</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>1320009.96</v>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Blumenau</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>9986075.83</v>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Tubarão</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>330186.78</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Lages</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>411928.32</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Campos Novos</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>2440498.86</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Concórdia</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>362020.23</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>São Carlos</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>15578.84</v>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Joinville</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>5100802.38</v>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Curitibanos</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>6158225.24</v>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Schroeder</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>3521922.69</v>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Irani</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>4690729.29</v>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Guaramirim</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>3493369.36</v>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -968,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -991,32 +529,6 @@
         <is>
           <t>Valor Total</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="D2" s="2" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>555</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>307394964.12</v>
       </c>
     </row>
   </sheetData>
